--- a/Education/Secondary_State_of_Origin.xlsx
+++ b/Education/Secondary_State_of_Origin.xlsx
@@ -537,7 +537,7 @@
         <v>7</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -554,7 +554,7 @@
         <v>8</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -571,7 +571,7 @@
         <v>9</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -622,7 +622,7 @@
         <v>12</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -656,7 +656,7 @@
         <v>14</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -673,7 +673,7 @@
         <v>15</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -690,7 +690,7 @@
         <v>16</v>
       </c>
       <c r="E11">
-        <v>54</v>
+        <v>617</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -707,7 +707,7 @@
         <v>17</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -724,7 +724,7 @@
         <v>18</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -741,7 +741,7 @@
         <v>19</v>
       </c>
       <c r="E14">
-        <v>76</v>
+        <v>519</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -775,7 +775,7 @@
         <v>21</v>
       </c>
       <c r="E16">
-        <v>22</v>
+        <v>339</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -809,7 +809,7 @@
         <v>23</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -877,7 +877,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -894,7 +894,7 @@
         <v>28</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -928,7 +928,7 @@
         <v>30</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -962,7 +962,7 @@
         <v>32</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -979,7 +979,7 @@
         <v>33</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -996,7 +996,7 @@
         <v>34</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1013,7 +1013,7 @@
         <v>35</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1030,7 +1030,7 @@
         <v>36</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1047,7 +1047,7 @@
         <v>37</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1149,7 +1149,7 @@
         <v>43</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1166,7 +1166,7 @@
         <v>7</v>
       </c>
       <c r="E39">
-        <v>5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1183,7 +1183,7 @@
         <v>8</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1200,7 +1200,7 @@
         <v>9</v>
       </c>
       <c r="E41">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1234,7 +1234,7 @@
         <v>11</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1251,7 +1251,7 @@
         <v>12</v>
       </c>
       <c r="E44">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1285,7 +1285,7 @@
         <v>14</v>
       </c>
       <c r="E46">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1302,7 +1302,7 @@
         <v>15</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1319,7 +1319,7 @@
         <v>16</v>
       </c>
       <c r="E48">
-        <v>29</v>
+        <v>355</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1336,7 +1336,7 @@
         <v>17</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1370,7 +1370,7 @@
         <v>19</v>
       </c>
       <c r="E51">
-        <v>37</v>
+        <v>243</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1404,7 +1404,7 @@
         <v>21</v>
       </c>
       <c r="E53">
-        <v>8</v>
+        <v>76</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1438,7 +1438,7 @@
         <v>23</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1506,7 +1506,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1523,7 +1523,7 @@
         <v>28</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1591,7 +1591,7 @@
         <v>32</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1625,7 +1625,7 @@
         <v>34</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1659,7 +1659,7 @@
         <v>36</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1676,7 +1676,7 @@
         <v>37</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -1710,7 +1710,7 @@
         <v>39</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -1778,7 +1778,7 @@
         <v>43</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -1795,7 +1795,7 @@
         <v>7</v>
       </c>
       <c r="E76">
-        <v>21</v>
+        <v>119</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -1812,7 +1812,7 @@
         <v>8</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -1829,7 +1829,7 @@
         <v>9</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -1880,7 +1880,7 @@
         <v>12</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -1914,7 +1914,7 @@
         <v>14</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -1931,7 +1931,7 @@
         <v>15</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -1948,7 +1948,7 @@
         <v>16</v>
       </c>
       <c r="E85">
-        <v>19</v>
+        <v>173</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -1965,7 +1965,7 @@
         <v>17</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -1999,7 +1999,7 @@
         <v>19</v>
       </c>
       <c r="E88">
-        <v>12</v>
+        <v>94</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2033,7 +2033,7 @@
         <v>21</v>
       </c>
       <c r="E90">
-        <v>28</v>
+        <v>228</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2067,7 +2067,7 @@
         <v>23</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2135,7 +2135,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2237,7 +2237,7 @@
         <v>33</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2305,7 +2305,7 @@
         <v>37</v>
       </c>
       <c r="E106">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2424,7 +2424,7 @@
         <v>7</v>
       </c>
       <c r="E113">
-        <v>4</v>
+        <v>107</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -2441,7 +2441,7 @@
         <v>8</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -2458,7 +2458,7 @@
         <v>9</v>
       </c>
       <c r="E115">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2475,7 +2475,7 @@
         <v>10</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2492,7 +2492,7 @@
         <v>11</v>
       </c>
       <c r="E117">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2509,7 +2509,7 @@
         <v>12</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -2526,7 +2526,7 @@
         <v>13</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -2543,7 +2543,7 @@
         <v>14</v>
       </c>
       <c r="E120">
-        <v>0</v>
+        <v>83</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -2560,7 +2560,7 @@
         <v>15</v>
       </c>
       <c r="E121">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -2577,7 +2577,7 @@
         <v>16</v>
       </c>
       <c r="E122">
-        <v>10</v>
+        <v>658</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -2594,7 +2594,7 @@
         <v>17</v>
       </c>
       <c r="E123">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -2628,7 +2628,7 @@
         <v>19</v>
       </c>
       <c r="E125">
-        <v>45</v>
+        <v>667</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -2662,7 +2662,7 @@
         <v>21</v>
       </c>
       <c r="E127">
-        <v>16</v>
+        <v>216</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -2696,7 +2696,7 @@
         <v>23</v>
       </c>
       <c r="E129">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -2747,7 +2747,7 @@
         <v>26</v>
       </c>
       <c r="E132">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -2764,7 +2764,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -2781,7 +2781,7 @@
         <v>28</v>
       </c>
       <c r="E134">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -2798,7 +2798,7 @@
         <v>29</v>
       </c>
       <c r="E135">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -2815,7 +2815,7 @@
         <v>30</v>
       </c>
       <c r="E136">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -2866,7 +2866,7 @@
         <v>33</v>
       </c>
       <c r="E139">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -2883,7 +2883,7 @@
         <v>34</v>
       </c>
       <c r="E140">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -2900,7 +2900,7 @@
         <v>35</v>
       </c>
       <c r="E141">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -2917,7 +2917,7 @@
         <v>36</v>
       </c>
       <c r="E142">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -2934,7 +2934,7 @@
         <v>37</v>
       </c>
       <c r="E143">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -2968,7 +2968,7 @@
         <v>39</v>
       </c>
       <c r="E145">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -3036,7 +3036,7 @@
         <v>43</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -3053,7 +3053,7 @@
         <v>7</v>
       </c>
       <c r="E150">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -3070,7 +3070,7 @@
         <v>8</v>
       </c>
       <c r="E151">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -3087,7 +3087,7 @@
         <v>9</v>
       </c>
       <c r="E152">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -3104,7 +3104,7 @@
         <v>10</v>
       </c>
       <c r="E153">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -3172,7 +3172,7 @@
         <v>14</v>
       </c>
       <c r="E157">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3189,7 +3189,7 @@
         <v>15</v>
       </c>
       <c r="E158">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3206,7 +3206,7 @@
         <v>16</v>
       </c>
       <c r="E159">
-        <v>68</v>
+        <v>179</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3223,7 +3223,7 @@
         <v>17</v>
       </c>
       <c r="E160">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3257,7 +3257,7 @@
         <v>19</v>
       </c>
       <c r="E162">
-        <v>170</v>
+        <v>274</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -3291,7 +3291,7 @@
         <v>21</v>
       </c>
       <c r="E164">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -3393,7 +3393,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3410,7 +3410,7 @@
         <v>28</v>
       </c>
       <c r="E171">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -3512,7 +3512,7 @@
         <v>34</v>
       </c>
       <c r="E177">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -3546,7 +3546,7 @@
         <v>36</v>
       </c>
       <c r="E179">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -3682,7 +3682,7 @@
         <v>7</v>
       </c>
       <c r="E187">
-        <v>16</v>
+        <v>349</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -3699,7 +3699,7 @@
         <v>8</v>
       </c>
       <c r="E188">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -3716,7 +3716,7 @@
         <v>9</v>
       </c>
       <c r="E189">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -3733,7 +3733,7 @@
         <v>10</v>
       </c>
       <c r="E190">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -3750,7 +3750,7 @@
         <v>11</v>
       </c>
       <c r="E191">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -3767,7 +3767,7 @@
         <v>12</v>
       </c>
       <c r="E192">
-        <v>9</v>
+        <v>116</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -3801,7 +3801,7 @@
         <v>14</v>
       </c>
       <c r="E194">
-        <v>5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -3818,7 +3818,7 @@
         <v>15</v>
       </c>
       <c r="E195">
-        <v>10</v>
+        <v>102</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -3835,7 +3835,7 @@
         <v>16</v>
       </c>
       <c r="E196">
-        <v>65</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -3852,7 +3852,7 @@
         <v>17</v>
       </c>
       <c r="E197">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -3869,7 +3869,7 @@
         <v>18</v>
       </c>
       <c r="E198">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -3886,7 +3886,7 @@
         <v>19</v>
       </c>
       <c r="E199">
-        <v>203</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -3903,7 +3903,7 @@
         <v>20</v>
       </c>
       <c r="E200">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -3920,7 +3920,7 @@
         <v>21</v>
       </c>
       <c r="E201">
-        <v>50</v>
+        <v>460</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -3954,7 +3954,7 @@
         <v>23</v>
       </c>
       <c r="E203">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -3971,7 +3971,7 @@
         <v>24</v>
       </c>
       <c r="E204">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -4022,7 +4022,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -4039,7 +4039,7 @@
         <v>28</v>
       </c>
       <c r="E208">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -4056,7 +4056,7 @@
         <v>29</v>
       </c>
       <c r="E209">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -4073,7 +4073,7 @@
         <v>30</v>
       </c>
       <c r="E210">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -4090,7 +4090,7 @@
         <v>31</v>
       </c>
       <c r="E211">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -4107,7 +4107,7 @@
         <v>32</v>
       </c>
       <c r="E212">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -4124,7 +4124,7 @@
         <v>33</v>
       </c>
       <c r="E213">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -4141,7 +4141,7 @@
         <v>34</v>
       </c>
       <c r="E214">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -4158,7 +4158,7 @@
         <v>35</v>
       </c>
       <c r="E215">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -4175,7 +4175,7 @@
         <v>36</v>
       </c>
       <c r="E216">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -4192,7 +4192,7 @@
         <v>37</v>
       </c>
       <c r="E217">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -4209,7 +4209,7 @@
         <v>38</v>
       </c>
       <c r="E218">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4226,7 +4226,7 @@
         <v>39</v>
       </c>
       <c r="E219">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -4277,7 +4277,7 @@
         <v>42</v>
       </c>
       <c r="E222">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -4294,7 +4294,7 @@
         <v>43</v>
       </c>
       <c r="E223">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -4311,7 +4311,7 @@
         <v>7</v>
       </c>
       <c r="E224">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -4328,7 +4328,7 @@
         <v>8</v>
       </c>
       <c r="E225">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -4345,7 +4345,7 @@
         <v>9</v>
       </c>
       <c r="E226">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -4396,7 +4396,7 @@
         <v>12</v>
       </c>
       <c r="E229">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -4430,7 +4430,7 @@
         <v>14</v>
       </c>
       <c r="E231">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -4447,7 +4447,7 @@
         <v>15</v>
       </c>
       <c r="E232">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -4464,7 +4464,7 @@
         <v>16</v>
       </c>
       <c r="E233">
-        <v>38</v>
+        <v>321</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -4481,7 +4481,7 @@
         <v>17</v>
       </c>
       <c r="E234">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -4498,7 +4498,7 @@
         <v>18</v>
       </c>
       <c r="E235">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -4515,7 +4515,7 @@
         <v>19</v>
       </c>
       <c r="E236">
-        <v>85</v>
+        <v>472</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -4549,7 +4549,7 @@
         <v>21</v>
       </c>
       <c r="E238">
-        <v>30</v>
+        <v>223</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -4634,7 +4634,7 @@
         <v>26</v>
       </c>
       <c r="E243">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -4651,7 +4651,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -4719,7 +4719,7 @@
         <v>31</v>
       </c>
       <c r="E248">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -4736,7 +4736,7 @@
         <v>32</v>
       </c>
       <c r="E249">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -4770,7 +4770,7 @@
         <v>34</v>
       </c>
       <c r="E251">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -4787,7 +4787,7 @@
         <v>35</v>
       </c>
       <c r="E252">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -4804,7 +4804,7 @@
         <v>36</v>
       </c>
       <c r="E253">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -4821,7 +4821,7 @@
         <v>37</v>
       </c>
       <c r="E254">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -4855,7 +4855,7 @@
         <v>39</v>
       </c>
       <c r="E256">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -4923,7 +4923,7 @@
         <v>43</v>
       </c>
       <c r="E260">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -4940,7 +4940,7 @@
         <v>7</v>
       </c>
       <c r="E261">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -4957,7 +4957,7 @@
         <v>8</v>
       </c>
       <c r="E262">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -4974,7 +4974,7 @@
         <v>9</v>
       </c>
       <c r="E263">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -5025,7 +5025,7 @@
         <v>12</v>
       </c>
       <c r="E266">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -5059,7 +5059,7 @@
         <v>14</v>
       </c>
       <c r="E268">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -5076,7 +5076,7 @@
         <v>15</v>
       </c>
       <c r="E269">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -5093,7 +5093,7 @@
         <v>16</v>
       </c>
       <c r="E270">
-        <v>7</v>
+        <v>281</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -5110,7 +5110,7 @@
         <v>17</v>
       </c>
       <c r="E271">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -5127,7 +5127,7 @@
         <v>18</v>
       </c>
       <c r="E272">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -5144,7 +5144,7 @@
         <v>19</v>
       </c>
       <c r="E273">
-        <v>39</v>
+        <v>365</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -5178,7 +5178,7 @@
         <v>21</v>
       </c>
       <c r="E275">
-        <v>16</v>
+        <v>77</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -5263,7 +5263,7 @@
         <v>26</v>
       </c>
       <c r="E280">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -5280,7 +5280,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -5314,7 +5314,7 @@
         <v>29</v>
       </c>
       <c r="E283">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -5331,7 +5331,7 @@
         <v>30</v>
       </c>
       <c r="E284">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -5348,7 +5348,7 @@
         <v>31</v>
       </c>
       <c r="E285">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -5382,7 +5382,7 @@
         <v>33</v>
       </c>
       <c r="E287">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288" spans="1:5">
@@ -5399,7 +5399,7 @@
         <v>34</v>
       </c>
       <c r="E288">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289" spans="1:5">
@@ -5433,7 +5433,7 @@
         <v>36</v>
       </c>
       <c r="E290">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -5450,7 +5450,7 @@
         <v>37</v>
       </c>
       <c r="E291">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="292" spans="1:5">
@@ -5484,7 +5484,7 @@
         <v>39</v>
       </c>
       <c r="E293">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="294" spans="1:5">
@@ -5518,7 +5518,7 @@
         <v>41</v>
       </c>
       <c r="E295">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296" spans="1:5">
@@ -5552,7 +5552,7 @@
         <v>43</v>
       </c>
       <c r="E297">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -5569,7 +5569,7 @@
         <v>7</v>
       </c>
       <c r="E298">
-        <v>40</v>
+        <v>341</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -5586,7 +5586,7 @@
         <v>8</v>
       </c>
       <c r="E299">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -5603,7 +5603,7 @@
         <v>9</v>
       </c>
       <c r="E300">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -5637,7 +5637,7 @@
         <v>11</v>
       </c>
       <c r="E302">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303" spans="1:5">
@@ -5654,7 +5654,7 @@
         <v>12</v>
       </c>
       <c r="E303">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -5688,7 +5688,7 @@
         <v>14</v>
       </c>
       <c r="E305">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -5705,7 +5705,7 @@
         <v>15</v>
       </c>
       <c r="E306">
-        <v>4</v>
+        <v>57</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -5722,7 +5722,7 @@
         <v>16</v>
       </c>
       <c r="E307">
-        <v>87</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -5739,7 +5739,7 @@
         <v>17</v>
       </c>
       <c r="E308">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="309" spans="1:5">
@@ -5773,7 +5773,7 @@
         <v>19</v>
       </c>
       <c r="E310">
-        <v>160</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="311" spans="1:5">
@@ -5807,7 +5807,7 @@
         <v>21</v>
       </c>
       <c r="E312">
-        <v>81</v>
+        <v>785</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -5824,7 +5824,7 @@
         <v>22</v>
       </c>
       <c r="E313">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -5841,7 +5841,7 @@
         <v>23</v>
       </c>
       <c r="E314">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -5875,7 +5875,7 @@
         <v>25</v>
       </c>
       <c r="E316">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317" spans="1:5">
@@ -5892,7 +5892,7 @@
         <v>26</v>
       </c>
       <c r="E317">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="318" spans="1:5">
@@ -5909,7 +5909,7 @@
         <v>27</v>
       </c>
       <c r="E318">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -5926,7 +5926,7 @@
         <v>28</v>
       </c>
       <c r="E319">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320" spans="1:5">
@@ -5960,7 +5960,7 @@
         <v>30</v>
       </c>
       <c r="E321">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="322" spans="1:5">
@@ -6011,7 +6011,7 @@
         <v>33</v>
       </c>
       <c r="E324">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -6028,7 +6028,7 @@
         <v>34</v>
       </c>
       <c r="E325">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -6045,7 +6045,7 @@
         <v>35</v>
       </c>
       <c r="E326">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -6062,7 +6062,7 @@
         <v>36</v>
       </c>
       <c r="E327">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="328" spans="1:5">
@@ -6079,7 +6079,7 @@
         <v>37</v>
       </c>
       <c r="E328">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -6113,7 +6113,7 @@
         <v>39</v>
       </c>
       <c r="E330">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -6181,7 +6181,7 @@
         <v>43</v>
       </c>
       <c r="E334">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="335" spans="1:5">
@@ -6198,7 +6198,7 @@
         <v>7</v>
       </c>
       <c r="E335">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="336" spans="1:5">
@@ -6232,7 +6232,7 @@
         <v>9</v>
       </c>
       <c r="E337">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -6249,7 +6249,7 @@
         <v>10</v>
       </c>
       <c r="E338">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -6283,7 +6283,7 @@
         <v>12</v>
       </c>
       <c r="E340">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -6317,7 +6317,7 @@
         <v>14</v>
       </c>
       <c r="E342">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -6334,7 +6334,7 @@
         <v>15</v>
       </c>
       <c r="E343">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -6351,7 +6351,7 @@
         <v>16</v>
       </c>
       <c r="E344">
-        <v>75</v>
+        <v>296</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -6385,7 +6385,7 @@
         <v>18</v>
       </c>
       <c r="E346">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -6402,7 +6402,7 @@
         <v>19</v>
       </c>
       <c r="E347">
-        <v>57</v>
+        <v>247</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -6436,7 +6436,7 @@
         <v>21</v>
       </c>
       <c r="E349">
-        <v>36</v>
+        <v>170</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -6538,7 +6538,7 @@
         <v>27</v>
       </c>
       <c r="E355">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -6555,7 +6555,7 @@
         <v>28</v>
       </c>
       <c r="E356">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -6572,7 +6572,7 @@
         <v>29</v>
       </c>
       <c r="E357">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -6640,7 +6640,7 @@
         <v>33</v>
       </c>
       <c r="E361">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="362" spans="1:5">
@@ -6691,7 +6691,7 @@
         <v>36</v>
       </c>
       <c r="E364">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -6708,7 +6708,7 @@
         <v>37</v>
       </c>
       <c r="E365">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -6827,7 +6827,7 @@
         <v>7</v>
       </c>
       <c r="E372">
-        <v>25</v>
+        <v>125</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -6861,7 +6861,7 @@
         <v>9</v>
       </c>
       <c r="E374">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="375" spans="1:5">
@@ -6912,7 +6912,7 @@
         <v>12</v>
       </c>
       <c r="E377">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -6946,7 +6946,7 @@
         <v>14</v>
       </c>
       <c r="E379">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -6963,7 +6963,7 @@
         <v>15</v>
       </c>
       <c r="E380">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -6980,7 +6980,7 @@
         <v>16</v>
       </c>
       <c r="E381">
-        <v>161</v>
+        <v>551</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -6997,7 +6997,7 @@
         <v>17</v>
       </c>
       <c r="E382">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -7014,7 +7014,7 @@
         <v>18</v>
       </c>
       <c r="E383">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -7031,7 +7031,7 @@
         <v>19</v>
       </c>
       <c r="E384">
-        <v>78</v>
+        <v>392</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -7065,7 +7065,7 @@
         <v>21</v>
       </c>
       <c r="E386">
-        <v>36</v>
+        <v>278</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -7116,7 +7116,7 @@
         <v>24</v>
       </c>
       <c r="E389">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -7167,7 +7167,7 @@
         <v>27</v>
       </c>
       <c r="E392">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -7201,7 +7201,7 @@
         <v>29</v>
       </c>
       <c r="E394">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="395" spans="1:5">
@@ -7252,7 +7252,7 @@
         <v>32</v>
       </c>
       <c r="E397">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="398" spans="1:5">
@@ -7269,7 +7269,7 @@
         <v>33</v>
       </c>
       <c r="E398">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="399" spans="1:5">
@@ -7286,7 +7286,7 @@
         <v>34</v>
       </c>
       <c r="E399">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="400" spans="1:5">
@@ -7303,7 +7303,7 @@
         <v>35</v>
       </c>
       <c r="E400">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="401" spans="1:5">
@@ -7320,7 +7320,7 @@
         <v>36</v>
       </c>
       <c r="E401">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="402" spans="1:5">
@@ -7337,7 +7337,7 @@
         <v>37</v>
       </c>
       <c r="E402">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="403" spans="1:5">
@@ -7439,7 +7439,7 @@
         <v>43</v>
       </c>
       <c r="E408">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="409" spans="1:5">
@@ -7456,7 +7456,7 @@
         <v>7</v>
       </c>
       <c r="E409">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="410" spans="1:5">
@@ -7490,7 +7490,7 @@
         <v>9</v>
       </c>
       <c r="E411">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="412" spans="1:5">
@@ -7541,7 +7541,7 @@
         <v>12</v>
       </c>
       <c r="E414">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="415" spans="1:5">
@@ -7575,7 +7575,7 @@
         <v>14</v>
       </c>
       <c r="E416">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="417" spans="1:5">
@@ -7592,7 +7592,7 @@
         <v>15</v>
       </c>
       <c r="E417">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -7609,7 +7609,7 @@
         <v>16</v>
       </c>
       <c r="E418">
-        <v>3</v>
+        <v>116</v>
       </c>
     </row>
     <row r="419" spans="1:5">
@@ -7626,7 +7626,7 @@
         <v>17</v>
       </c>
       <c r="E419">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="420" spans="1:5">
@@ -7660,7 +7660,7 @@
         <v>19</v>
       </c>
       <c r="E421">
-        <v>2</v>
+        <v>123</v>
       </c>
     </row>
     <row r="422" spans="1:5">
@@ -7694,7 +7694,7 @@
         <v>21</v>
       </c>
       <c r="E423">
-        <v>42</v>
+        <v>375</v>
       </c>
     </row>
     <row r="424" spans="1:5">
@@ -7796,7 +7796,7 @@
         <v>27</v>
       </c>
       <c r="E429">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="430" spans="1:5">
@@ -7813,7 +7813,7 @@
         <v>28</v>
       </c>
       <c r="E430">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="431" spans="1:5">
@@ -7830,7 +7830,7 @@
         <v>29</v>
       </c>
       <c r="E431">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="432" spans="1:5">
@@ -7847,7 +7847,7 @@
         <v>30</v>
       </c>
       <c r="E432">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="433" spans="1:5">
@@ -7864,7 +7864,7 @@
         <v>31</v>
       </c>
       <c r="E433">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="434" spans="1:5">
@@ -7881,7 +7881,7 @@
         <v>32</v>
       </c>
       <c r="E434">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="435" spans="1:5">
@@ -7898,7 +7898,7 @@
         <v>33</v>
       </c>
       <c r="E435">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="436" spans="1:5">
@@ -7915,7 +7915,7 @@
         <v>34</v>
       </c>
       <c r="E436">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -7932,7 +7932,7 @@
         <v>35</v>
       </c>
       <c r="E437">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="438" spans="1:5">
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="E438">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="439" spans="1:5">
@@ -7966,7 +7966,7 @@
         <v>37</v>
       </c>
       <c r="E439">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -8000,7 +8000,7 @@
         <v>39</v>
       </c>
       <c r="E441">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="442" spans="1:5">
@@ -8068,7 +8068,7 @@
         <v>43</v>
       </c>
       <c r="E445">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="446" spans="1:5">
@@ -8085,7 +8085,7 @@
         <v>7</v>
       </c>
       <c r="E446">
-        <v>2</v>
+        <v>417</v>
       </c>
     </row>
     <row r="447" spans="1:5">
@@ -8102,7 +8102,7 @@
         <v>8</v>
       </c>
       <c r="E447">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="448" spans="1:5">
@@ -8119,7 +8119,7 @@
         <v>9</v>
       </c>
       <c r="E448">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="449" spans="1:5">
@@ -8136,7 +8136,7 @@
         <v>10</v>
       </c>
       <c r="E449">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450" spans="1:5">
@@ -8153,7 +8153,7 @@
         <v>11</v>
       </c>
       <c r="E450">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="451" spans="1:5">
@@ -8170,7 +8170,7 @@
         <v>12</v>
       </c>
       <c r="E451">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="452" spans="1:5">
@@ -8204,7 +8204,7 @@
         <v>14</v>
       </c>
       <c r="E453">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="454" spans="1:5">
@@ -8221,7 +8221,7 @@
         <v>15</v>
       </c>
       <c r="E454">
-        <v>1</v>
+        <v>69</v>
       </c>
     </row>
     <row r="455" spans="1:5">
@@ -8238,7 +8238,7 @@
         <v>16</v>
       </c>
       <c r="E455">
-        <v>48</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="456" spans="1:5">
@@ -8255,7 +8255,7 @@
         <v>17</v>
       </c>
       <c r="E456">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="457" spans="1:5">
@@ -8272,7 +8272,7 @@
         <v>18</v>
       </c>
       <c r="E457">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="458" spans="1:5">
@@ -8289,7 +8289,7 @@
         <v>19</v>
       </c>
       <c r="E458">
-        <v>48</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="459" spans="1:5">
@@ -8306,7 +8306,7 @@
         <v>20</v>
       </c>
       <c r="E459">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="460" spans="1:5">
@@ -8323,7 +8323,7 @@
         <v>21</v>
       </c>
       <c r="E460">
-        <v>11</v>
+        <v>962</v>
       </c>
     </row>
     <row r="461" spans="1:5">
@@ -8357,7 +8357,7 @@
         <v>23</v>
       </c>
       <c r="E462">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="463" spans="1:5">
@@ -8374,7 +8374,7 @@
         <v>24</v>
       </c>
       <c r="E463">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="464" spans="1:5">
@@ -8425,7 +8425,7 @@
         <v>27</v>
       </c>
       <c r="E466">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="467" spans="1:5">
@@ -8459,7 +8459,7 @@
         <v>29</v>
       </c>
       <c r="E468">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="469" spans="1:5">
@@ -8476,7 +8476,7 @@
         <v>30</v>
       </c>
       <c r="E469">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="470" spans="1:5">
@@ -8510,7 +8510,7 @@
         <v>32</v>
       </c>
       <c r="E471">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="472" spans="1:5">
@@ -8527,7 +8527,7 @@
         <v>33</v>
       </c>
       <c r="E472">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="473" spans="1:5">
@@ -8544,7 +8544,7 @@
         <v>34</v>
       </c>
       <c r="E473">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="474" spans="1:5">
@@ -8561,7 +8561,7 @@
         <v>35</v>
       </c>
       <c r="E474">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="475" spans="1:5">
@@ -8578,7 +8578,7 @@
         <v>36</v>
       </c>
       <c r="E475">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="476" spans="1:5">
@@ -8595,7 +8595,7 @@
         <v>37</v>
       </c>
       <c r="E476">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="477" spans="1:5">
@@ -8629,7 +8629,7 @@
         <v>39</v>
       </c>
       <c r="E478">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="479" spans="1:5">
@@ -8697,7 +8697,7 @@
         <v>43</v>
       </c>
       <c r="E482">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="483" spans="1:5">
@@ -8714,7 +8714,7 @@
         <v>7</v>
       </c>
       <c r="E483">
-        <v>16</v>
+        <v>171</v>
       </c>
     </row>
     <row r="484" spans="1:5">
@@ -8731,7 +8731,7 @@
         <v>8</v>
       </c>
       <c r="E484">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="485" spans="1:5">
@@ -8748,7 +8748,7 @@
         <v>9</v>
       </c>
       <c r="E485">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="486" spans="1:5">
@@ -8782,7 +8782,7 @@
         <v>11</v>
       </c>
       <c r="E487">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="488" spans="1:5">
@@ -8799,7 +8799,7 @@
         <v>12</v>
       </c>
       <c r="E488">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="489" spans="1:5">
@@ -8833,7 +8833,7 @@
         <v>14</v>
       </c>
       <c r="E490">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="491" spans="1:5">
@@ -8850,7 +8850,7 @@
         <v>15</v>
       </c>
       <c r="E491">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="492" spans="1:5">
@@ -8867,7 +8867,7 @@
         <v>16</v>
       </c>
       <c r="E492">
-        <v>65</v>
+        <v>795</v>
       </c>
     </row>
     <row r="493" spans="1:5">
@@ -8884,7 +8884,7 @@
         <v>17</v>
       </c>
       <c r="E493">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="494" spans="1:5">
@@ -8901,7 +8901,7 @@
         <v>18</v>
       </c>
       <c r="E494">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="495" spans="1:5">
@@ -8918,7 +8918,7 @@
         <v>19</v>
       </c>
       <c r="E495">
-        <v>203</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="496" spans="1:5">
@@ -8952,7 +8952,7 @@
         <v>21</v>
       </c>
       <c r="E497">
-        <v>50</v>
+        <v>395</v>
       </c>
     </row>
     <row r="498" spans="1:5">
@@ -8986,7 +8986,7 @@
         <v>23</v>
       </c>
       <c r="E499">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="500" spans="1:5">
@@ -9054,7 +9054,7 @@
         <v>27</v>
       </c>
       <c r="E503">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="504" spans="1:5">
@@ -9088,7 +9088,7 @@
         <v>29</v>
       </c>
       <c r="E505">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="506" spans="1:5">
@@ -9139,7 +9139,7 @@
         <v>32</v>
       </c>
       <c r="E508">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="509" spans="1:5">
@@ -9156,7 +9156,7 @@
         <v>33</v>
       </c>
       <c r="E509">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="510" spans="1:5">
@@ -9173,7 +9173,7 @@
         <v>34</v>
       </c>
       <c r="E510">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="511" spans="1:5">
@@ -9190,7 +9190,7 @@
         <v>35</v>
       </c>
       <c r="E511">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="512" spans="1:5">
@@ -9207,7 +9207,7 @@
         <v>36</v>
       </c>
       <c r="E512">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="513" spans="1:5">
@@ -9224,7 +9224,7 @@
         <v>37</v>
       </c>
       <c r="E513">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="514" spans="1:5">
@@ -9258,7 +9258,7 @@
         <v>39</v>
       </c>
       <c r="E515">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="516" spans="1:5">
@@ -9326,7 +9326,7 @@
         <v>43</v>
       </c>
       <c r="E519">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="520" spans="1:5">
@@ -9343,7 +9343,7 @@
         <v>7</v>
       </c>
       <c r="E520">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="521" spans="1:5">
@@ -9377,7 +9377,7 @@
         <v>9</v>
       </c>
       <c r="E522">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="523" spans="1:5">
@@ -9411,7 +9411,7 @@
         <v>11</v>
       </c>
       <c r="E524">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="525" spans="1:5">
@@ -9428,7 +9428,7 @@
         <v>12</v>
       </c>
       <c r="E525">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="526" spans="1:5">
@@ -9462,7 +9462,7 @@
         <v>14</v>
       </c>
       <c r="E527">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="528" spans="1:5">
@@ -9479,7 +9479,7 @@
         <v>15</v>
       </c>
       <c r="E528">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="529" spans="1:5">
@@ -9496,7 +9496,7 @@
         <v>16</v>
       </c>
       <c r="E529">
-        <v>6</v>
+        <v>399</v>
       </c>
     </row>
     <row r="530" spans="1:5">
@@ -9513,7 +9513,7 @@
         <v>17</v>
       </c>
       <c r="E530">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="531" spans="1:5">
@@ -9547,7 +9547,7 @@
         <v>19</v>
       </c>
       <c r="E532">
-        <v>6</v>
+        <v>564</v>
       </c>
     </row>
     <row r="533" spans="1:5">
@@ -9581,7 +9581,7 @@
         <v>21</v>
       </c>
       <c r="E534">
-        <v>1</v>
+        <v>149</v>
       </c>
     </row>
     <row r="535" spans="1:5">
@@ -9649,7 +9649,7 @@
         <v>25</v>
       </c>
       <c r="E538">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="539" spans="1:5">
@@ -9683,7 +9683,7 @@
         <v>27</v>
       </c>
       <c r="E540">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="541" spans="1:5">
@@ -9717,7 +9717,7 @@
         <v>29</v>
       </c>
       <c r="E542">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="543" spans="1:5">
@@ -9802,7 +9802,7 @@
         <v>34</v>
       </c>
       <c r="E547">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="548" spans="1:5">
@@ -9836,7 +9836,7 @@
         <v>36</v>
       </c>
       <c r="E549">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="550" spans="1:5">
@@ -9853,7 +9853,7 @@
         <v>37</v>
       </c>
       <c r="E550">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="551" spans="1:5">
@@ -9972,7 +9972,7 @@
         <v>7</v>
       </c>
       <c r="E557">
-        <v>49</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="558" spans="1:5">
@@ -9989,7 +9989,7 @@
         <v>8</v>
       </c>
       <c r="E558">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="559" spans="1:5">
@@ -10006,7 +10006,7 @@
         <v>9</v>
       </c>
       <c r="E559">
-        <v>3</v>
+        <v>234</v>
       </c>
     </row>
     <row r="560" spans="1:5">
@@ -10023,7 +10023,7 @@
         <v>10</v>
       </c>
       <c r="E560">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="561" spans="1:5">
@@ -10040,7 +10040,7 @@
         <v>11</v>
       </c>
       <c r="E561">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="562" spans="1:5">
@@ -10057,7 +10057,7 @@
         <v>12</v>
       </c>
       <c r="E562">
-        <v>1</v>
+        <v>93</v>
       </c>
     </row>
     <row r="563" spans="1:5">
@@ -10074,7 +10074,7 @@
         <v>13</v>
       </c>
       <c r="E563">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="564" spans="1:5">
@@ -10091,7 +10091,7 @@
         <v>14</v>
       </c>
       <c r="E564">
-        <v>3</v>
+        <v>128</v>
       </c>
     </row>
     <row r="565" spans="1:5">
@@ -10108,7 +10108,7 @@
         <v>15</v>
       </c>
       <c r="E565">
-        <v>10</v>
+        <v>342</v>
       </c>
     </row>
     <row r="566" spans="1:5">
@@ -10125,7 +10125,7 @@
         <v>16</v>
       </c>
       <c r="E566">
-        <v>29</v>
+        <v>2659</v>
       </c>
     </row>
     <row r="567" spans="1:5">
@@ -10142,7 +10142,7 @@
         <v>17</v>
       </c>
       <c r="E567">
-        <v>6</v>
+        <v>66</v>
       </c>
     </row>
     <row r="568" spans="1:5">
@@ -10159,7 +10159,7 @@
         <v>18</v>
       </c>
       <c r="E568">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="569" spans="1:5">
@@ -10176,7 +10176,7 @@
         <v>19</v>
       </c>
       <c r="E569">
-        <v>131</v>
+        <v>5235</v>
       </c>
     </row>
     <row r="570" spans="1:5">
@@ -10193,7 +10193,7 @@
         <v>20</v>
       </c>
       <c r="E570">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="571" spans="1:5">
@@ -10210,7 +10210,7 @@
         <v>21</v>
       </c>
       <c r="E571">
-        <v>137</v>
+        <v>2982</v>
       </c>
     </row>
     <row r="572" spans="1:5">
@@ -10227,7 +10227,7 @@
         <v>22</v>
       </c>
       <c r="E572">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="573" spans="1:5">
@@ -10244,7 +10244,7 @@
         <v>23</v>
       </c>
       <c r="E573">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="574" spans="1:5">
@@ -10261,7 +10261,7 @@
         <v>24</v>
       </c>
       <c r="E574">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="575" spans="1:5">
@@ -10278,7 +10278,7 @@
         <v>25</v>
       </c>
       <c r="E575">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="576" spans="1:5">
@@ -10312,7 +10312,7 @@
         <v>27</v>
       </c>
       <c r="E577">
-        <v>0</v>
+        <v>126</v>
       </c>
     </row>
     <row r="578" spans="1:5">
@@ -10329,7 +10329,7 @@
         <v>28</v>
       </c>
       <c r="E578">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="579" spans="1:5">
@@ -10346,7 +10346,7 @@
         <v>29</v>
       </c>
       <c r="E579">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="580" spans="1:5">
@@ -10363,7 +10363,7 @@
         <v>30</v>
       </c>
       <c r="E580">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="581" spans="1:5">
@@ -10380,7 +10380,7 @@
         <v>31</v>
       </c>
       <c r="E581">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="582" spans="1:5">
@@ -10397,7 +10397,7 @@
         <v>32</v>
       </c>
       <c r="E582">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="583" spans="1:5">
@@ -10414,7 +10414,7 @@
         <v>33</v>
       </c>
       <c r="E583">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="584" spans="1:5">
@@ -10431,7 +10431,7 @@
         <v>34</v>
       </c>
       <c r="E584">
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
     <row r="585" spans="1:5">
@@ -10448,7 +10448,7 @@
         <v>35</v>
       </c>
       <c r="E585">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="586" spans="1:5">
@@ -10465,7 +10465,7 @@
         <v>36</v>
       </c>
       <c r="E586">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="587" spans="1:5">
@@ -10482,7 +10482,7 @@
         <v>37</v>
       </c>
       <c r="E587">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="588" spans="1:5">
@@ -10499,7 +10499,7 @@
         <v>38</v>
       </c>
       <c r="E588">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="589" spans="1:5">
@@ -10516,7 +10516,7 @@
         <v>39</v>
       </c>
       <c r="E589">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="590" spans="1:5">
@@ -10533,7 +10533,7 @@
         <v>40</v>
       </c>
       <c r="E590">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="591" spans="1:5">
@@ -10567,7 +10567,7 @@
         <v>42</v>
       </c>
       <c r="E592">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="593" spans="1:5">
@@ -10584,7 +10584,7 @@
         <v>43</v>
       </c>
       <c r="E593">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="594" spans="1:5">
@@ -10601,7 +10601,7 @@
         <v>7</v>
       </c>
       <c r="E594">
-        <v>9</v>
+        <v>358</v>
       </c>
     </row>
     <row r="595" spans="1:5">
@@ -10618,7 +10618,7 @@
         <v>8</v>
       </c>
       <c r="E595">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="596" spans="1:5">
@@ -10635,7 +10635,7 @@
         <v>9</v>
       </c>
       <c r="E596">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="597" spans="1:5">
@@ -10686,7 +10686,7 @@
         <v>12</v>
       </c>
       <c r="E599">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="600" spans="1:5">
@@ -10720,7 +10720,7 @@
         <v>14</v>
       </c>
       <c r="E601">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="602" spans="1:5">
@@ -10737,7 +10737,7 @@
         <v>15</v>
       </c>
       <c r="E602">
-        <v>4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="603" spans="1:5">
@@ -10754,7 +10754,7 @@
         <v>16</v>
       </c>
       <c r="E603">
-        <v>6</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="604" spans="1:5">
@@ -10771,7 +10771,7 @@
         <v>17</v>
       </c>
       <c r="E604">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="605" spans="1:5">
@@ -10788,7 +10788,7 @@
         <v>18</v>
       </c>
       <c r="E605">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="606" spans="1:5">
@@ -10805,7 +10805,7 @@
         <v>19</v>
       </c>
       <c r="E606">
-        <v>58</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="607" spans="1:5">
@@ -10839,7 +10839,7 @@
         <v>21</v>
       </c>
       <c r="E608">
-        <v>44</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="609" spans="1:5">
@@ -10890,7 +10890,7 @@
         <v>24</v>
       </c>
       <c r="E611">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="612" spans="1:5">
@@ -10907,7 +10907,7 @@
         <v>25</v>
       </c>
       <c r="E612">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="613" spans="1:5">
@@ -10941,7 +10941,7 @@
         <v>27</v>
       </c>
       <c r="E614">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="615" spans="1:5">
@@ -10958,7 +10958,7 @@
         <v>28</v>
       </c>
       <c r="E615">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="616" spans="1:5">
@@ -10992,7 +10992,7 @@
         <v>30</v>
       </c>
       <c r="E617">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="618" spans="1:5">
@@ -11009,7 +11009,7 @@
         <v>31</v>
       </c>
       <c r="E618">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="619" spans="1:5">
@@ -11043,7 +11043,7 @@
         <v>33</v>
       </c>
       <c r="E620">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="621" spans="1:5">
@@ -11060,7 +11060,7 @@
         <v>34</v>
       </c>
       <c r="E621">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="622" spans="1:5">
@@ -11077,7 +11077,7 @@
         <v>35</v>
       </c>
       <c r="E622">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="623" spans="1:5">
@@ -11094,7 +11094,7 @@
         <v>36</v>
       </c>
       <c r="E623">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="624" spans="1:5">
@@ -11111,7 +11111,7 @@
         <v>37</v>
       </c>
       <c r="E624">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="625" spans="1:5">
@@ -11213,7 +11213,7 @@
         <v>43</v>
       </c>
       <c r="E630">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="631" spans="1:5">
@@ -11230,7 +11230,7 @@
         <v>7</v>
       </c>
       <c r="E631">
-        <v>1</v>
+        <v>225</v>
       </c>
     </row>
     <row r="632" spans="1:5">
@@ -11264,7 +11264,7 @@
         <v>9</v>
       </c>
       <c r="E633">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="634" spans="1:5">
@@ -11298,7 +11298,7 @@
         <v>11</v>
       </c>
       <c r="E635">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="636" spans="1:5">
@@ -11315,7 +11315,7 @@
         <v>12</v>
       </c>
       <c r="E636">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="637" spans="1:5">
@@ -11349,7 +11349,7 @@
         <v>14</v>
       </c>
       <c r="E638">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="639" spans="1:5">
@@ -11366,7 +11366,7 @@
         <v>15</v>
       </c>
       <c r="E639">
-        <v>4</v>
+        <v>116</v>
       </c>
     </row>
     <row r="640" spans="1:5">
@@ -11383,7 +11383,7 @@
         <v>16</v>
       </c>
       <c r="E640">
-        <v>35</v>
+        <v>601</v>
       </c>
     </row>
     <row r="641" spans="1:5">
@@ -11400,7 +11400,7 @@
         <v>17</v>
       </c>
       <c r="E641">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="642" spans="1:5">
@@ -11434,7 +11434,7 @@
         <v>19</v>
       </c>
       <c r="E643">
-        <v>53</v>
+        <v>605</v>
       </c>
     </row>
     <row r="644" spans="1:5">
@@ -11468,7 +11468,7 @@
         <v>21</v>
       </c>
       <c r="E645">
-        <v>59</v>
+        <v>765</v>
       </c>
     </row>
     <row r="646" spans="1:5">
@@ -11536,7 +11536,7 @@
         <v>25</v>
       </c>
       <c r="E649">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="650" spans="1:5">
@@ -11570,7 +11570,7 @@
         <v>27</v>
       </c>
       <c r="E651">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="652" spans="1:5">
@@ -11587,7 +11587,7 @@
         <v>28</v>
       </c>
       <c r="E652">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="653" spans="1:5">
@@ -11604,7 +11604,7 @@
         <v>29</v>
       </c>
       <c r="E653">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="654" spans="1:5">
@@ -11621,7 +11621,7 @@
         <v>30</v>
       </c>
       <c r="E654">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="655" spans="1:5">
@@ -11655,7 +11655,7 @@
         <v>32</v>
       </c>
       <c r="E656">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="657" spans="1:5">
@@ -11672,7 +11672,7 @@
         <v>33</v>
       </c>
       <c r="E657">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="658" spans="1:5">
@@ -11689,7 +11689,7 @@
         <v>34</v>
       </c>
       <c r="E658">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="659" spans="1:5">
@@ -11706,7 +11706,7 @@
         <v>35</v>
       </c>
       <c r="E659">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="660" spans="1:5">
@@ -11723,7 +11723,7 @@
         <v>36</v>
       </c>
       <c r="E660">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="661" spans="1:5">
@@ -11740,7 +11740,7 @@
         <v>37</v>
       </c>
       <c r="E661">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="662" spans="1:5">
@@ -11774,7 +11774,7 @@
         <v>39</v>
       </c>
       <c r="E663">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="664" spans="1:5">
@@ -11859,7 +11859,7 @@
         <v>7</v>
       </c>
       <c r="E668">
-        <v>14</v>
+        <v>46</v>
       </c>
     </row>
     <row r="669" spans="1:5">
@@ -11893,7 +11893,7 @@
         <v>9</v>
       </c>
       <c r="E670">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="671" spans="1:5">
@@ -11927,7 +11927,7 @@
         <v>11</v>
       </c>
       <c r="E672">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="673" spans="1:5">
@@ -11944,7 +11944,7 @@
         <v>12</v>
       </c>
       <c r="E673">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="674" spans="1:5">
@@ -11978,7 +11978,7 @@
         <v>14</v>
       </c>
       <c r="E675">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="676" spans="1:5">
@@ -11995,7 +11995,7 @@
         <v>15</v>
       </c>
       <c r="E676">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="677" spans="1:5">
@@ -12012,7 +12012,7 @@
         <v>16</v>
       </c>
       <c r="E677">
-        <v>20</v>
+        <v>151</v>
       </c>
     </row>
     <row r="678" spans="1:5">
@@ -12029,7 +12029,7 @@
         <v>17</v>
       </c>
       <c r="E678">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="679" spans="1:5">
@@ -12063,7 +12063,7 @@
         <v>19</v>
       </c>
       <c r="E680">
-        <v>21</v>
+        <v>261</v>
       </c>
     </row>
     <row r="681" spans="1:5">
@@ -12097,7 +12097,7 @@
         <v>21</v>
       </c>
       <c r="E682">
-        <v>20</v>
+        <v>120</v>
       </c>
     </row>
     <row r="683" spans="1:5">
@@ -12199,7 +12199,7 @@
         <v>27</v>
       </c>
       <c r="E688">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="689" spans="1:5">
@@ -12233,7 +12233,7 @@
         <v>29</v>
       </c>
       <c r="E690">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="691" spans="1:5">
@@ -12284,7 +12284,7 @@
         <v>32</v>
       </c>
       <c r="E693">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="694" spans="1:5">
@@ -12624,7 +12624,7 @@
         <v>15</v>
       </c>
       <c r="E713">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="714" spans="1:5">
@@ -12641,7 +12641,7 @@
         <v>16</v>
       </c>
       <c r="E714">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="715" spans="1:5">
@@ -12692,7 +12692,7 @@
         <v>19</v>
       </c>
       <c r="E717">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="718" spans="1:5">
@@ -12726,7 +12726,7 @@
         <v>21</v>
       </c>
       <c r="E719">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="720" spans="1:5">
@@ -12828,7 +12828,7 @@
         <v>27</v>
       </c>
       <c r="E725">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="726" spans="1:5">
@@ -13117,7 +13117,7 @@
         <v>7</v>
       </c>
       <c r="E742">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="743" spans="1:5">
@@ -13134,7 +13134,7 @@
         <v>8</v>
       </c>
       <c r="E743">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="744" spans="1:5">
@@ -13151,7 +13151,7 @@
         <v>9</v>
       </c>
       <c r="E744">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="745" spans="1:5">
@@ -13202,7 +13202,7 @@
         <v>12</v>
       </c>
       <c r="E747">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="748" spans="1:5">
@@ -13253,7 +13253,7 @@
         <v>15</v>
       </c>
       <c r="E750">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="751" spans="1:5">
@@ -13270,7 +13270,7 @@
         <v>16</v>
       </c>
       <c r="E751">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="752" spans="1:5">
@@ -13321,7 +13321,7 @@
         <v>19</v>
       </c>
       <c r="E754">
-        <v>2</v>
+        <v>70</v>
       </c>
     </row>
     <row r="755" spans="1:5">
@@ -13355,7 +13355,7 @@
         <v>21</v>
       </c>
       <c r="E756">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="757" spans="1:5">
@@ -13457,7 +13457,7 @@
         <v>27</v>
       </c>
       <c r="E762">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="763" spans="1:5">
